--- a/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Armand marche à la ferme avec maman. Un chien. Armand dit le nom : le chien. Le cri : ouah. Une vache. Le nom : la vache. Le cri : meuh. Un coq. Le nom : le coq. Le cri : cocorico. Maman dit : on nomme l'animal. On nomme le cri. Armand répète : chien, ouah. Vache, meuh. Coq, cocorico.</t>
+          <t>Armand marche à la ferme avec maman. Un chien. Armand dit le nom : le chien. Le cri : ouah. Une vache. Le nom : la vache. Le cri : meuh. Un coq. Le nom : le coq. Le cri : cocorico. On nomme l'animal. On nomme le cri. Armand répète : chien, ouah. Vache, meuh. Coq, cocorico.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Armand marche à la ferme avec maman. Un chien. Armand dit le nom : le chien. Le cri : ouah. Une vache. Le nom : la vache. Le cri : meuh. Un coq. Le nom : le coq. Le cri : cocorico.
+maman|On nomme l'animal. On nomme le cri.
+narrateur|Armand répète : chien, ouah. Vache, meuh. Coq, cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Armand entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Armand a dit le nom de l'animal. Il a dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le seau. Armand salue le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Armand répète : chien, ouah. Vache, meuh. Coq, cocorico.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Armand entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Armand a dit le nom de l'animal. Il a dit le cri.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1841,11 @@
           <t>narrateur|Maman range le seau. Armand salue le chien.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Armand nomme les cris de la basse-cour</t>
+          <t>L'oie trop bruyante</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut voir l'oie de la basse-cour. L'oie cacarde trop fort. Elles reculent près de maman et regardent d'ici.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Armand marche à la ferme avec maman. Un chien. Armand dit le nom : le chien. Le cri : ouah. Une vache. Le nom : la vache. Le cri : meuh. Un coq. Le nom : le coq. Le cri : cocorico. On nomme l'animal. On nomme le cri. Armand répète : chien, ouah. Vache, meuh. Coq, cocorico.</t>
+          <t>Des plumes blanches collent au grillage chaud. Un grain de maïs roule dans la poussière. La basse-cour sent le son et l'eau tiède. Une gamelle de fer brille au soleil. Tu vois les plumes, Nina ? Oui. Je veux l'oie. L'oie blanche ? Celle qui crie. En ce moment, Nina s'approche du grillage. Le métal est chaud sous ses doigts. Un cou long se lève derrière le fil. L'oie ouvre le bec. Ça ça, très fort. Oh. Elle cacarde. Le cri tape les oreilles de Nina. L'oie avance, les ailes un peu ouvertes. Elle est trop bruyante. On recule près de moi ? Oui. Nina lâche le grillage. Elle vient contre la jambe de maman. Le tissu du pantalon est frais. On reste avec l'adulte, près des animaux. On écoute d'ici. D'accord. L'oie cacarde encore, plus loin. Ça ça, moins fort maintenant. Ça ça. C'est son cri. Une plume blanche s'envole vers Nina. Elle ne la chasse pas. Elle reste contre maman. Le soleil tape encore le grillage. On reste ici. Oui. Nina sent le son chaud de la cour. Une plume blanche se colle à sa chaussette. Une plume. On la laisse. Nina ne s'approche plus du fil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Armand marche à la ferme avec maman. Un chien. Armand dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; : le chien. Le cri : ouah. Une vache. Le nom : la vache. Le cri : meuh. Un coq. Le nom : le coq. Le cri : cocorico. Maman dit : on nomme l'animal. On nomme le cri. Armand répète : chien, ouah. Vache, meuh. Coq, cocorico.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des plumes blanches collent au grillage chaud. Un grain de maïs roule dans la poussière. La basse-cour sent le son et l'eau tiède. Une gamelle de fer brille au soleil. Tu vois les plumes, Nina ? Oui. Je veux l'oie. L'oie blanche ? Celle qui crie. En ce moment, Nina s'approche du grillage. Le métal est chaud sous ses doigts. Un cou long se lève derrière le fil. L'oie ouvre le bec. Ça ça, très fort. Oh. Elle cacarde. Le cri tape les oreilles de Nina. L'oie avance, les ailes un peu ouvertes. Elle est trop bruyante. On recule près de moi ? Oui. Nina lâche le grillage. Elle vient contre la jambe de maman. Le tissu du pantalon est frais. On reste avec l'adulte, près des animaux. On écoute d'ici. D'accord. L'oie cacarde encore, plus loin. Ça ça, moins fort maintenant. Ça ça. C'est son cri. Une plume blanche s'envole vers Nina. Elle ne la chasse pas. Elle reste contre maman. Le soleil tape encore le grillage. On reste ici. Oui. Nina sent le son chaud de la cour. Une plume blanche se colle à sa chaussette. Une plume. On la laisse. Nina ne s'approche plus du fil.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,9 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Armand marche à la ferme avec maman. Un chien. Armand dit le nom : le chien. Le cri : ouah. Une vache. Le nom : la vache. Le cri : meuh. Un coq. Le nom : le coq. Le cri : cocorico.
-maman|On nomme l'animal. On nomme le cri.
-narrateur|Armand répète : chien, ouah. Vache, meuh. Coq, cocorico.</t>
+          <t>narrateur|Des plumes blanches collent au grillage chaud.
+narrateur|Un grain de maïs roule dans la poussière.
+narrateur|La basse-cour sent le son et l'eau tiède.
+narrateur|Une gamelle de fer brille au soleil.
+maman|Tu vois les plumes, Nina ?
+enfant-f|Oui.
+enfant-f|Je veux l'oie.
+maman|L'oie blanche ?
+enfant-f|Celle qui crie.
+narrateur|En ce moment, Nina s'approche du grillage.
+narrateur|Le métal est chaud sous ses doigts.
+narrateur|Un cou long se lève derrière le fil.
+narrateur|L'oie ouvre le bec.
+narrateur|Ça ça, très fort.
+enfant-f|Oh.
+maman|Elle cacarde.
+narrateur|Le cri tape les oreilles de Nina.
+narrateur|L'oie avance, les ailes un peu ouvertes.
+enfant-f|Elle est trop bruyante.
+maman|On recule près de moi ?
+enfant-f|Oui.
+narrateur|Nina lâche le grillage.
+narrateur|Elle vient contre la jambe de maman.
+narrateur|Le tissu du pantalon est frais.
+maman|On reste avec l'adulte, près des animaux.
+maman|On écoute d'ici.
+enfant-f|D'accord.
+narrateur|L'oie cacarde encore, plus loin.
+narrateur|Ça ça, moins fort maintenant.
+enfant-f|Ça ça.
+maman|C'est son cri.
+narrateur|Une plume blanche s'envole vers Nina.
+narrateur|Elle ne la chasse pas.
+narrateur|Elle reste contre maman.
+narrateur|Le soleil tape encore le grillage.
+enfant-f|On reste ici.
+maman|Oui.
+narrateur|Nina sent le son chaud de la cour.
+narrateur|Une plume blanche se colle à sa chaussette.
+enfant-f|Une plume.
+maman|On la laisse.
+narrateur|Nina ne s'approche plus du fil.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,12 +1397,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Armand entend un bruit. C'est quoi ?</t>
+          <t>Nina entend ça ça. Quel est le cri de l'oie ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Armand entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina entend ça ça. Quel est le cri de l'oie ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1361,12 +1412,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>le cri</t>
+          <t>cacarde</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le cri | le chien | meuh | le coq</t>
+          <t>cacarde | ça ça | le cri | l'oie | elle cacarde</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1432,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On nomme l'animal et le cri. C'est quoi ?</t>
+          <t>L'oie cacarde. Quel est le cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1481,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1553,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Armand entend un bruit. C'est quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina entend ça ça.
+narrateur|Quel est le cri de l'oie ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1581,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Armand a dit le nom de l'animal. Il a dit le cri.</t>
+          <t>L'oie picore le grain, le cou plié. Ses pattes orangées tapent la terre. Je la vois d'ici. Merci d'être revenue près de moi. On reste avec l'adulte. Elle cacarde. Oui. Ça ça. Nina pose la main sur le pantalon. Le cri ne tape plus autant. On la regarde d'ici ? Oui. Le grillage fait un petit tic au soleil. La gamelle de fer reste vide un moment. L'oie s'éloigne vers l'auge.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Armand a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. Il a dit le cri.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'oie picore le grain, le cou plié. Ses pattes orangées tapent la terre. Je la vois d'ici. Merci d'être revenue près de moi. On reste avec l'adulte. Elle cacarde. Oui. Ça ça. Nina pose la main sur le pantalon. Le cri ne tape plus autant. On la regarde d'ici ? Oui. Le grillage fait un petit tic au soleil. La gamelle de fer reste vide un moment. L'oie s'éloigne vers l'auge.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1598,7 +1649,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,10 +1725,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Armand a dit le nom de l'animal. Il a dit le cri.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|L'oie picore le grain, le cou plié.
+narrateur|Ses pattes orangées tapent la terre.
+enfant-f|Je la vois d'ici.
+maman|Merci d'être revenue près de moi.
+maman|On reste avec l'adulte.
+enfant-f|Elle cacarde.
+maman|Oui.
+maman|Ça ça.
+narrateur|Nina pose la main sur le pantalon.
+narrateur|Le cri ne tape plus autant.
+maman|On la regarde d'ici ?
+enfant-f|Oui.
+narrateur|Le grillage fait un petit tic au soleil.
+narrateur|La gamelle de fer reste vide un moment.
+narrateur|L'oie s'éloigne vers l'auge.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Armand salue le chien.</t>
+          <t>Une autre plume colle au fil chaud. Nina ne s'approche plus. Elle est moins forte. Tu voulais l'oie. On l'a vue, près de moi. Le maïs roule encore d'un doigt. L'oie le suit, tout blanche. Ça ça. C'est son cri. Nina souffle. Ses épaules redescendent. Tu es restée avec moi. Le grain de maïs a disparu. L'oie boit à l'auge, le cou plié. Elle ne crie plus. On peut rester encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le seau. Armand salue le chien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une autre plume colle au fil chaud. Nina ne s'approche plus. Elle est moins forte. Tu voulais l'oie. On l'a vue, près de moi. Le maïs roule encore d'un doigt. L'oie le suit, tout blanche. Ça ça. C'est son cri. Nina souffle. Ses épaules redescendent. Tu es restée avec moi. Le grain de maïs a disparu. L'oie boit à l'auge, le cou plié. Elle ne crie plus. On peut rester encore un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,7 +1834,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1838,7 +1902,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau. Armand salue le chien.</t>
+          <t>narrateur|Une autre plume colle au fil chaud.
+narrateur|Nina ne s'approche plus.
+enfant-f|Elle est moins forte.
+maman|Tu voulais l'oie.
+maman|On l'a vue, près de moi.
+narrateur|Le maïs roule encore d'un doigt.
+narrateur|L'oie le suit, tout blanche.
+enfant-f|Ça ça.
+maman|C'est son cri.
+narrateur|Nina souffle.
+narrateur|Ses épaules redescendent.
+maman|Tu es restée avec moi.
+narrateur|Le grain de maïs a disparu.
+narrateur|L'oie boit à l'auge, le cou plié.
+enfant-f|Elle ne crie plus.
+maman|On peut rester encore un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1870,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'oie picore au loin, toute blanche. Nina tient la main de maman. On l'a vue. Oui. Une plume blanche dort encore au grillage.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'oie picore au loin, toute blanche. Nina tient la main de maman. On l'a vue. Oui. Une plume blanche dort encore au grillage.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1931,14 +2010,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,10 +2089,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|L'oie picore au loin, toute blanche.
+narrateur|Nina tient la main de maman.
+enfant-f|On l'a vue.
+maman|Oui.
+narrateur|Une plume blanche dort encore au grillage.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>basse-cour, grillage chaud, plumes blanches</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Armand, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
